--- a/implementation_evaluation_forms/001_youth_climate_policy_understanding_survey--implementation_evaluation_forms.xlsx
+++ b/implementation_evaluation_forms/001_youth_climate_policy_understanding_survey--implementation_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1033,8 +1033,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'high'}</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'low'}</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'national'}</t>
+          <t>national</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'national'}</t>
+          <t>national</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'local'}</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'local'}</t>
+          <t>local</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'global'}</t>
+          <t>global</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'global'}</t>
+          <t>global</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'family'}</t>
+          <t>family</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'friends'}</t>
+          <t>friends</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'friends'}</t>
+          <t>friends</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'school'}</t>
+          <t>school</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'school'}</t>
+          <t>school</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'social media'}</t>
+          <t>social media</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'internet'}</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'internet'}</t>
+          <t>internet</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'government'}</t>
+          <t>government</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'government'}</t>
+          <t>government</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'strong'}</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'strong'}</t>
+          <t>strong</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'weak'}</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'weak'}</t>
+          <t>weak</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'reduce_consumption'}</t>
+          <t>reduce_consumption</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'reduce consumption'}</t>
+          <t>reduce consumption</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'change_consumption_habits'}</t>
+          <t>change_consumption_habits</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'change consumption habits'}</t>
+          <t>change consumption habits</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'invest_in_re'}</t>
+          <t>invest_in_re</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'invest in re'}</t>
+          <t>invest in re</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'transition_to_renew'}</t>
+          <t>transition_to_renew</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'transition to renew'}</t>
+          <t>transition to renew</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'government'}</t>
+          <t>government</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'government'}</t>
+          <t>government</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'social media'}</t>
+          <t>social media</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'school'}</t>
+          <t>school</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'school'}</t>
+          <t>school</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'family'}</t>
+          <t>family</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'friends'}</t>
+          <t>friends</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'friends'}</t>
+          <t>friends</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'good'}</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
